--- a/resources/UserDetails_prod.xlsx
+++ b/resources/UserDetails_prod.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>Email</t>
   </si>
@@ -93,6 +93,15 @@
   </si>
   <si>
     <t>RustyHickle@yopmail.com</t>
+  </si>
+  <si>
+    <t>CarmenLueilwitzMD@yopmail.com</t>
+  </si>
+  <si>
+    <t>AlbertoWisozk@yopmail.com</t>
+  </si>
+  <si>
+    <t>JulesJohnsonPhD@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -1252,7 +1261,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1365,6 +1374,21 @@
         <v>21</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/resources/UserDetails_prod.xlsx
+++ b/resources/UserDetails_prod.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Email</t>
   </si>
@@ -96,6 +96,9 @@
   </si>
   <si>
     <t>EldonTrantow@yopmail.com</t>
+  </si>
+  <si>
+    <t>JeramyWest@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -1255,7 +1258,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1373,6 +1376,11 @@
         <v>22</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/resources/UserDetails_prod.xlsx
+++ b/resources/UserDetails_prod.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Email</t>
   </si>
@@ -99,6 +99,18 @@
   </si>
   <si>
     <t>JeramyWest@yopmail.com</t>
+  </si>
+  <si>
+    <t>AlexKoch@yopmail.com</t>
+  </si>
+  <si>
+    <t>KarrenBarton@yopmail.com</t>
+  </si>
+  <si>
+    <t>EddieArmstrong@yopmail.com</t>
+  </si>
+  <si>
+    <t>AgripinaBartoletti@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -1258,7 +1270,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1381,6 +1393,26 @@
         <v>23</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/resources/UserDetails_prod.xlsx
+++ b/resources/UserDetails_prod.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Email</t>
   </si>
@@ -111,6 +111,15 @@
   </si>
   <si>
     <t>AgripinaBartoletti@yopmail.com</t>
+  </si>
+  <si>
+    <t>ClaraKassulke@yopmail.com</t>
+  </si>
+  <si>
+    <t>IluminadaParisianV@yopmail.com</t>
+  </si>
+  <si>
+    <t>ShanaSawayn@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -1270,7 +1279,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1413,6 +1422,21 @@
         <v>27</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
